--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Reports\Camera Reports\Dashboard\3L Solutions\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\DEN Camera System\3L Solutions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4115874C-2A03-4328-92CD-9A1893A629FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{01E0E032-EF3E-42E8-9AD3-DEBA758D3BAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="945" windowWidth="23280" windowHeight="14535" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRIVE-ALERTS" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2912" uniqueCount="1009">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3247" uniqueCount="1109">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
@@ -2809,6 +2809,9 @@
     <t>03/09/26 15:50 PDT</t>
   </si>
   <si>
+    <t>03/16/26 04:07 PDT</t>
+  </si>
+  <si>
     <t>03/06/26 06:59 PST</t>
   </si>
   <si>
@@ -2974,6 +2977,9 @@
     <t>03/11/26 05:18 PDT</t>
   </si>
   <si>
+    <t>03/16/26 04:06 PDT</t>
+  </si>
+  <si>
     <t>03/11/26 02:16 PDT</t>
   </si>
   <si>
@@ -3022,24 +3028,18 @@
     <t>03/13/26 04:00 PDT</t>
   </si>
   <si>
-    <t>03/13/26 06:30 PDT</t>
-  </si>
-  <si>
-    <t>LANE-CONDUCT</t>
-  </si>
-  <si>
-    <t>1.2mi W of La Cañada Flintridge CA</t>
+    <t>03/13/26 05:59 PDT</t>
   </si>
   <si>
     <t>03/13/26 09:51 PDT</t>
   </si>
   <si>
-    <t>03/13/26 11:01 PDT</t>
-  </si>
-  <si>
     <t>03/13/26 11:40 PDT</t>
   </si>
   <si>
+    <t>03/14/26 02:29 PDT</t>
+  </si>
+  <si>
     <t>03/14/26 02:33 PDT</t>
   </si>
   <si>
@@ -3047,6 +3047,306 @@
   </si>
   <si>
     <t>03/14/26 04:37 PDT</t>
+  </si>
+  <si>
+    <t>03/14/26 07:32 PDT</t>
+  </si>
+  <si>
+    <t>1.5mi SE of South San Jose Hills CA</t>
+  </si>
+  <si>
+    <t>03/16/26 02:20 PDT</t>
+  </si>
+  <si>
+    <t>03/16/26 02:23 PDT</t>
+  </si>
+  <si>
+    <t>03/16/26 03:52 PDT</t>
+  </si>
+  <si>
+    <t>3.9mi W of East Los Angeles CA</t>
+  </si>
+  <si>
+    <t>03/16/26 04:38 PDT</t>
+  </si>
+  <si>
+    <t>03/16/26 04:59 PDT</t>
+  </si>
+  <si>
+    <t>10.5mi SW of Arvin CA</t>
+  </si>
+  <si>
+    <t>03/16/26 06:43 PDT</t>
+  </si>
+  <si>
+    <t>03/16/26 06:48 PDT</t>
+  </si>
+  <si>
+    <t>8mi NW of Castaic CA</t>
+  </si>
+  <si>
+    <t>03/16/26 07:35 PDT</t>
+  </si>
+  <si>
+    <t>1.3mi W of Avocado Heights CA</t>
+  </si>
+  <si>
+    <t>03/16/26 07:41 PDT</t>
+  </si>
+  <si>
+    <t>3.5mi NW of Burbank CA</t>
+  </si>
+  <si>
+    <t>03/16/26 08:29 PDT</t>
+  </si>
+  <si>
+    <t>03/16/26 10:05 PDT</t>
+  </si>
+  <si>
+    <t>03/16/26 10:58 PDT</t>
+  </si>
+  <si>
+    <t>03/16/26 12:29 PDT</t>
+  </si>
+  <si>
+    <t>3.8mi SE of West Carson CA</t>
+  </si>
+  <si>
+    <t>03/16/26 13:55 PDT</t>
+  </si>
+  <si>
+    <t>03/16/26 14:29 PDT</t>
+  </si>
+  <si>
+    <t>03/17/26 03:28 PDT</t>
+  </si>
+  <si>
+    <t>03/17/26 03:46 PDT</t>
+  </si>
+  <si>
+    <t>2.6mi S of East Rancho Dominguez CA</t>
+  </si>
+  <si>
+    <t>03/18/26 04:40 PDT</t>
+  </si>
+  <si>
+    <t>03/17/26 04:42 PDT</t>
+  </si>
+  <si>
+    <t>03/17/26 04:44 PDT</t>
+  </si>
+  <si>
+    <t>6.9mi NW of Castaic CA</t>
+  </si>
+  <si>
+    <t>03/17/26 05:05 PDT</t>
+  </si>
+  <si>
+    <t>1mi NE of Maywood CA</t>
+  </si>
+  <si>
+    <t>03/17/26 05:57 PDT</t>
+  </si>
+  <si>
+    <t>03/17/26 06:44 PDT</t>
+  </si>
+  <si>
+    <t>7.5mi NW of Castaic CA</t>
+  </si>
+  <si>
+    <t>03/17/26 08:06 PDT</t>
+  </si>
+  <si>
+    <t>03/17/26 08:46 PDT</t>
+  </si>
+  <si>
+    <t>2.4mi S of Pomona CA</t>
+  </si>
+  <si>
+    <t>03/17/26 09:02 PDT</t>
+  </si>
+  <si>
+    <t>03/17/26 09:05 PDT</t>
+  </si>
+  <si>
+    <t>03/17/26 09:36 PDT</t>
+  </si>
+  <si>
+    <t>3.3mi SE of Kingsburg CA</t>
+  </si>
+  <si>
+    <t>03/17/26 10:29 PDT</t>
+  </si>
+  <si>
+    <t>0.9mi S of Earlimart CA</t>
+  </si>
+  <si>
+    <t>03/17/26 12:14 PDT</t>
+  </si>
+  <si>
+    <t>1mi E of Avocado Heights CA</t>
+  </si>
+  <si>
+    <t>03/18/26 04:43 PDT</t>
+  </si>
+  <si>
+    <t>03/19/26 01:10 PDT</t>
+  </si>
+  <si>
+    <t>03/17/26 12:15 PDT</t>
+  </si>
+  <si>
+    <t>4.8mi E of East Niles CA</t>
+  </si>
+  <si>
+    <t>Non-Coachable</t>
+  </si>
+  <si>
+    <t>03/18/26 04:52 PDT</t>
+  </si>
+  <si>
+    <t>03/18/26 03:12 PDT</t>
+  </si>
+  <si>
+    <t>03/18/26 06:29 PDT</t>
+  </si>
+  <si>
+    <t>8.4mi NW of Castaic CA</t>
+  </si>
+  <si>
+    <t>3.2mi S of San Fernando CA</t>
+  </si>
+  <si>
+    <t>03/18/26 06:50 PDT</t>
+  </si>
+  <si>
+    <t>03/18/26 11:02 PDT</t>
+  </si>
+  <si>
+    <t>03/18/26 11:58 PDT</t>
+  </si>
+  <si>
+    <t>03/18/26 12:00 PDT</t>
+  </si>
+  <si>
+    <t>03/19/26 01:44 PDT</t>
+  </si>
+  <si>
+    <t>21.1mi S of Arvin CA</t>
+  </si>
+  <si>
+    <t>03/19/26 02:22 PDT</t>
+  </si>
+  <si>
+    <t>0.9mi NE of Castaic CA</t>
+  </si>
+  <si>
+    <t>03/20/26 17:49 PDT</t>
+  </si>
+  <si>
+    <t>03/19/26 03:08 PDT</t>
+  </si>
+  <si>
+    <t>03/19/26 03:09 PDT</t>
+  </si>
+  <si>
+    <t>1.4mi N of Huntington Park CA</t>
+  </si>
+  <si>
+    <t>03/19/26 05:29 PDT</t>
+  </si>
+  <si>
+    <t>6.3mi NW of Castaic CA</t>
+  </si>
+  <si>
+    <t>03/19/26 05:59 PDT</t>
+  </si>
+  <si>
+    <t>0.6mi S of Pasadena CA</t>
+  </si>
+  <si>
+    <t>03/19/26 07:01 PDT</t>
+  </si>
+  <si>
+    <t>03/19/26 07:06 PDT</t>
+  </si>
+  <si>
+    <t>03/19/26 10:08 PDT</t>
+  </si>
+  <si>
+    <t>03/19/26 10:31 PDT</t>
+  </si>
+  <si>
+    <t>2.5mi N of San Fernando CA</t>
+  </si>
+  <si>
+    <t>03/19/26 10:59 PDT</t>
+  </si>
+  <si>
+    <t>3.4mi N of Huntington Park CA</t>
+  </si>
+  <si>
+    <t>03/19/26 11:56 PDT</t>
+  </si>
+  <si>
+    <t>03/19/26 12:29 PDT</t>
+  </si>
+  <si>
+    <t>03/19/26 12:59 PDT</t>
+  </si>
+  <si>
+    <t>03/20/26 03:13 PDT</t>
+  </si>
+  <si>
+    <t>03/20/26 07:00 PDT</t>
+  </si>
+  <si>
+    <t>1.7mi E of La Habra CA</t>
+  </si>
+  <si>
+    <t>03/20/26 11:43 PDT</t>
+  </si>
+  <si>
+    <t>03/20/26 12:04 PDT</t>
+  </si>
+  <si>
+    <t>Miguel Mora</t>
+  </si>
+  <si>
+    <t>6.7mi SW of Lamont CA</t>
+  </si>
+  <si>
+    <t>03/20/26 12:07 PDT</t>
+  </si>
+  <si>
+    <t>03/21/26 07:32 PDT</t>
+  </si>
+  <si>
+    <t>0.6mi NE of Maywood CA</t>
+  </si>
+  <si>
+    <t>03/21/26 08:07 PDT</t>
+  </si>
+  <si>
+    <t>03/21/26 08:39 PDT</t>
+  </si>
+  <si>
+    <t>1.5mi SW of Norwalk CA</t>
+  </si>
+  <si>
+    <t>03/21/26 09:26 PDT</t>
+  </si>
+  <si>
+    <t>03/21/26 10:50 PDT</t>
+  </si>
+  <si>
+    <t>2.7mi S of Ontario CA</t>
+  </si>
+  <si>
+    <t>03/21/26 13:07 PDT</t>
+  </si>
+  <si>
+    <t>3.8mi N of Stevenson Ranch CA</t>
   </si>
 </sst>
 </file>
@@ -3408,7 +3708,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M536"/>
+  <dimension ref="A1:M600"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="13" width="15" customWidth="1"/>
@@ -18934,11 +19234,13 @@
       <c r="L484" s="3" t="s">
         <v>928</v>
       </c>
-      <c r="M484" s="3"/>
+      <c r="M484" s="3" t="s">
+        <v>929</v>
+      </c>
     </row>
     <row r="485" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A485" s="3" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B485" s="3" t="s">
         <v>31</v>
@@ -18953,7 +19255,7 @@
         <v>28</v>
       </c>
       <c r="F485" s="3" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="G485" s="3"/>
       <c r="H485" s="3">
@@ -18969,7 +19271,7 @@
     </row>
     <row r="486" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A486" s="3" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B486" s="3" t="s">
         <v>124</v>
@@ -18984,7 +19286,7 @@
         <v>58</v>
       </c>
       <c r="F486" s="3" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="G486" s="3"/>
       <c r="H486" s="3">
@@ -19002,7 +19304,7 @@
     </row>
     <row r="487" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A487" s="3" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B487" s="3" t="s">
         <v>31</v>
@@ -19017,7 +19319,7 @@
         <v>28</v>
       </c>
       <c r="F487" s="3" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="G487" s="3"/>
       <c r="H487" s="3">
@@ -19033,7 +19335,7 @@
     </row>
     <row r="488" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A488" s="3" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B488" s="3" t="s">
         <v>31</v>
@@ -19048,7 +19350,7 @@
         <v>28</v>
       </c>
       <c r="F488" s="3" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="G488" s="3"/>
       <c r="H488" s="3">
@@ -19064,7 +19366,7 @@
     </row>
     <row r="489" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A489" s="3" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B489" s="3" t="s">
         <v>100</v>
@@ -19079,7 +19381,7 @@
         <v>55</v>
       </c>
       <c r="F489" s="3" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="G489" s="3"/>
       <c r="H489" s="3">
@@ -19095,7 +19397,7 @@
     </row>
     <row r="490" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A490" s="3" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B490" s="3" t="s">
         <v>21</v>
@@ -19124,7 +19426,7 @@
     </row>
     <row r="491" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A491" s="3" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B491" s="3" t="s">
         <v>112</v>
@@ -19139,7 +19441,7 @@
         <v>55</v>
       </c>
       <c r="F491" s="3" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="G491" s="3"/>
       <c r="H491" s="3">
@@ -19155,7 +19457,7 @@
     </row>
     <row r="492" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A492" s="3" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B492" s="3" t="s">
         <v>112</v>
@@ -19170,7 +19472,7 @@
         <v>568</v>
       </c>
       <c r="F492" s="3" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="G492" s="3"/>
       <c r="H492" s="3">
@@ -19186,7 +19488,7 @@
     </row>
     <row r="493" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A493" s="3" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B493" s="3" t="s">
         <v>21</v>
@@ -19201,7 +19503,7 @@
         <v>58</v>
       </c>
       <c r="F493" s="3" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="G493" s="3"/>
       <c r="H493" s="3"/>
@@ -19215,7 +19517,7 @@
     </row>
     <row r="494" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A494" s="3" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B494" s="3" t="s">
         <v>21</v>
@@ -19244,7 +19546,7 @@
     </row>
     <row r="495" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A495" s="3" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B495" s="3" t="s">
         <v>124</v>
@@ -19259,7 +19561,7 @@
         <v>58</v>
       </c>
       <c r="F495" s="3" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="G495" s="3"/>
       <c r="H495" s="3">
@@ -19275,7 +19577,7 @@
     </row>
     <row r="496" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A496" s="3" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B496" s="3" t="s">
         <v>124</v>
@@ -19304,7 +19606,7 @@
     </row>
     <row r="497" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A497" s="3" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B497" s="3" t="s">
         <v>112</v>
@@ -19319,7 +19621,7 @@
         <v>58</v>
       </c>
       <c r="F497" s="3" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="G497" s="3"/>
       <c r="H497" s="3">
@@ -19335,7 +19637,7 @@
     </row>
     <row r="498" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A498" s="3" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B498" s="3" t="s">
         <v>21</v>
@@ -19350,7 +19652,7 @@
         <v>17</v>
       </c>
       <c r="F498" s="3" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="G498" s="3"/>
       <c r="H498" s="3"/>
@@ -19364,7 +19666,7 @@
     </row>
     <row r="499" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A499" s="3" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B499" s="3" t="s">
         <v>21</v>
@@ -19379,7 +19681,7 @@
         <v>58</v>
       </c>
       <c r="F499" s="3" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="G499" s="3"/>
       <c r="H499" s="3"/>
@@ -19393,7 +19695,7 @@
     </row>
     <row r="500" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A500" s="3" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B500" s="3" t="s">
         <v>100</v>
@@ -19408,7 +19710,7 @@
         <v>58</v>
       </c>
       <c r="F500" s="3" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="G500" s="3"/>
       <c r="H500" s="3"/>
@@ -19422,7 +19724,7 @@
     </row>
     <row r="501" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A501" s="3" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B501" s="3" t="s">
         <v>100</v>
@@ -19437,7 +19739,7 @@
         <v>58</v>
       </c>
       <c r="F501" s="3" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="G501" s="3"/>
       <c r="H501" s="3">
@@ -19453,7 +19755,7 @@
     </row>
     <row r="502" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A502" s="3" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B502" s="3" t="s">
         <v>21</v>
@@ -19468,7 +19770,7 @@
         <v>58</v>
       </c>
       <c r="F502" s="3" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="G502" s="3"/>
       <c r="H502" s="3"/>
@@ -19482,7 +19784,7 @@
     </row>
     <row r="503" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A503" s="3" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B503" s="3" t="s">
         <v>124</v>
@@ -19515,7 +19817,7 @@
     </row>
     <row r="504" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A504" s="3" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B504" s="3" t="s">
         <v>21</v>
@@ -19530,7 +19832,7 @@
         <v>17</v>
       </c>
       <c r="F504" s="3" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="G504" s="3"/>
       <c r="H504" s="3"/>
@@ -19544,7 +19846,7 @@
     </row>
     <row r="505" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A505" s="3" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B505" s="3" t="s">
         <v>21</v>
@@ -19559,7 +19861,7 @@
         <v>58</v>
       </c>
       <c r="F505" s="3" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="G505" s="3"/>
       <c r="H505" s="3"/>
@@ -19573,7 +19875,7 @@
     </row>
     <row r="506" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A506" s="3" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B506" s="3" t="s">
         <v>25</v>
@@ -19604,13 +19906,13 @@
         <v>36</v>
       </c>
       <c r="L506" s="3" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="M506" s="3"/>
     </row>
     <row r="507" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A507" s="3" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B507" s="3" t="s">
         <v>25</v>
@@ -19625,7 +19927,7 @@
         <v>28</v>
       </c>
       <c r="F507" s="3" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="G507" s="3" t="s">
         <v>34</v>
@@ -19643,13 +19945,13 @@
         <v>36</v>
       </c>
       <c r="L507" s="3" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="M507" s="3"/>
     </row>
     <row r="508" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A508" s="3" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B508" s="3" t="s">
         <v>16</v>
@@ -19680,7 +19982,7 @@
     </row>
     <row r="509" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A509" s="3" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B509" s="3" t="s">
         <v>21</v>
@@ -19695,7 +19997,7 @@
         <v>58</v>
       </c>
       <c r="F509" s="3" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="G509" s="3"/>
       <c r="H509" s="3">
@@ -19711,7 +20013,7 @@
     </row>
     <row r="510" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A510" s="3" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B510" s="3" t="s">
         <v>112</v>
@@ -19726,7 +20028,7 @@
         <v>280</v>
       </c>
       <c r="F510" s="3" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="G510" s="3"/>
       <c r="H510" s="3">
@@ -19742,7 +20044,7 @@
     </row>
     <row r="511" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A511" s="3" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="B511" s="3" t="s">
         <v>21</v>
@@ -19773,7 +20075,7 @@
     </row>
     <row r="512" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A512" s="3" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B512" s="3" t="s">
         <v>124</v>
@@ -19804,7 +20106,7 @@
     </row>
     <row r="513" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A513" s="3" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B513" s="3" t="s">
         <v>21</v>
@@ -19835,7 +20137,7 @@
     </row>
     <row r="514" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A514" s="3" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B514" s="3" t="s">
         <v>21</v>
@@ -19866,7 +20168,7 @@
     </row>
     <row r="515" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A515" s="3" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B515" s="3" t="s">
         <v>25</v>
@@ -19897,13 +20199,13 @@
         <v>36</v>
       </c>
       <c r="L515" s="3" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="M515" s="3"/>
     </row>
     <row r="516" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A516" s="3" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="B516" s="3" t="s">
         <v>25</v>
@@ -19918,7 +20220,7 @@
         <v>45</v>
       </c>
       <c r="F516" s="3" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="G516" s="3" t="s">
         <v>34</v>
@@ -19936,13 +20238,15 @@
         <v>36</v>
       </c>
       <c r="L516" s="3" t="s">
-        <v>983</v>
-      </c>
-      <c r="M516" s="3"/>
+        <v>984</v>
+      </c>
+      <c r="M516" s="3" t="s">
+        <v>985</v>
+      </c>
     </row>
     <row r="517" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A517" s="3" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="B517" s="3" t="s">
         <v>16</v>
@@ -19973,7 +20277,7 @@
     </row>
     <row r="518" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A518" s="3" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="B518" s="3" t="s">
         <v>115</v>
@@ -19982,13 +20286,13 @@
         <v>193270</v>
       </c>
       <c r="D518" s="3">
-        <v>5396166131</v>
+        <v>5396071853</v>
       </c>
       <c r="E518" s="3" t="s">
         <v>58</v>
       </c>
       <c r="F518" s="3" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="G518" s="3"/>
       <c r="H518" s="3">
@@ -20004,7 +20308,7 @@
     </row>
     <row r="519" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A519" s="3" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="B519" s="3" t="s">
         <v>115</v>
@@ -20013,13 +20317,13 @@
         <v>193270</v>
       </c>
       <c r="D519" s="3">
-        <v>5396071853</v>
+        <v>5396166131</v>
       </c>
       <c r="E519" s="3" t="s">
         <v>58</v>
       </c>
       <c r="F519" s="3" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="G519" s="3"/>
       <c r="H519" s="3">
@@ -20035,7 +20339,7 @@
     </row>
     <row r="520" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A520" s="3" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="B520" s="3" t="s">
         <v>124</v>
@@ -20066,7 +20370,7 @@
     </row>
     <row r="521" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A521" s="3" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="B521" s="3" t="s">
         <v>21</v>
@@ -20097,7 +20401,7 @@
     </row>
     <row r="522" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A522" s="3" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="B522" s="3" t="s">
         <v>16</v>
@@ -20112,7 +20416,7 @@
         <v>17</v>
       </c>
       <c r="F522" s="3" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="G522" s="3"/>
       <c r="H522" s="3">
@@ -20128,7 +20432,7 @@
     </row>
     <row r="523" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A523" s="3" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="B523" s="3" t="s">
         <v>112</v>
@@ -20143,7 +20447,7 @@
         <v>58</v>
       </c>
       <c r="F523" s="3" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="G523" s="3"/>
       <c r="H523" s="3">
@@ -20159,7 +20463,7 @@
     </row>
     <row r="524" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A524" s="3" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="B524" s="3" t="s">
         <v>21</v>
@@ -20190,7 +20494,7 @@
     </row>
     <row r="525" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A525" s="3" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="B525" s="3" t="s">
         <v>112</v>
@@ -20221,7 +20525,7 @@
     </row>
     <row r="526" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A526" s="3" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="B526" s="3" t="s">
         <v>124</v>
@@ -20236,7 +20540,7 @@
         <v>58</v>
       </c>
       <c r="F526" s="3" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="G526" s="3"/>
       <c r="H526" s="3"/>
@@ -20250,7 +20554,7 @@
     </row>
     <row r="527" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A527" s="3" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="B527" s="3" t="s">
         <v>21</v>
@@ -20281,7 +20585,7 @@
     </row>
     <row r="528" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A528" s="3" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="B528" s="3" t="s">
         <v>16</v>
@@ -20312,7 +20616,7 @@
     </row>
     <row r="529" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A529" s="3" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="B529" s="3" t="s">
         <v>21</v>
@@ -20343,22 +20647,22 @@
     </row>
     <row r="530" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A530" s="3" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="B530" s="3" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="C530" s="3">
-        <v>596008</v>
+        <v>436998</v>
       </c>
       <c r="D530" s="3">
-        <v>5397469715</v>
+        <v>5407295154</v>
       </c>
       <c r="E530" s="3" t="s">
-        <v>1001</v>
+        <v>58</v>
       </c>
       <c r="F530" s="3" t="s">
-        <v>1002</v>
+        <v>512</v>
       </c>
       <c r="G530" s="3"/>
       <c r="H530" s="3"/>
@@ -20412,17 +20716,17 @@
         <v>436998</v>
       </c>
       <c r="D532" s="3">
-        <v>5399466090</v>
+        <v>5399816806</v>
       </c>
       <c r="E532" s="3" t="s">
         <v>22</v>
       </c>
       <c r="F532" s="3" t="s">
-        <v>53</v>
+        <v>364</v>
       </c>
       <c r="G532" s="3"/>
       <c r="H532" s="3">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I532" s="3"/>
       <c r="J532" s="3" t="s">
@@ -20443,17 +20747,17 @@
         <v>436998</v>
       </c>
       <c r="D533" s="3">
-        <v>5399816806</v>
+        <v>5411257983</v>
       </c>
       <c r="E533" s="3" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="F533" s="3" t="s">
-        <v>364</v>
+        <v>23</v>
       </c>
       <c r="G533" s="3"/>
       <c r="H533" s="3">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I533" s="3"/>
       <c r="J533" s="3" t="s">
@@ -20555,6 +20859,2012 @@
       <c r="K536" s="3"/>
       <c r="L536" s="3"/>
       <c r="M536" s="3"/>
+    </row>
+    <row r="537" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A537" s="3" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B537" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C537" s="3">
+        <v>436998</v>
+      </c>
+      <c r="D537" s="3">
+        <v>5403668732</v>
+      </c>
+      <c r="E537" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F537" s="3" t="s">
+        <v>1010</v>
+      </c>
+      <c r="G537" s="3"/>
+      <c r="H537" s="3">
+        <v>50</v>
+      </c>
+      <c r="I537" s="3">
+        <v>65</v>
+      </c>
+      <c r="J537" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K537" s="3"/>
+      <c r="L537" s="3"/>
+      <c r="M537" s="3"/>
+    </row>
+    <row r="538" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A538" s="3" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B538" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C538" s="3">
+        <v>436998</v>
+      </c>
+      <c r="D538" s="3">
+        <v>5411748747</v>
+      </c>
+      <c r="E538" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F538" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G538" s="3"/>
+      <c r="H538" s="3">
+        <v>36</v>
+      </c>
+      <c r="I538" s="3"/>
+      <c r="J538" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K538" s="3"/>
+      <c r="L538" s="3"/>
+      <c r="M538" s="3"/>
+    </row>
+    <row r="539" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A539" s="3" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B539" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C539" s="3">
+        <v>436998</v>
+      </c>
+      <c r="D539" s="3">
+        <v>5411754410</v>
+      </c>
+      <c r="E539" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F539" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G539" s="3"/>
+      <c r="H539" s="3">
+        <v>6</v>
+      </c>
+      <c r="I539" s="3"/>
+      <c r="J539" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K539" s="3"/>
+      <c r="L539" s="3"/>
+      <c r="M539" s="3"/>
+    </row>
+    <row r="540" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A540" s="3" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B540" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C540" s="3">
+        <v>436998</v>
+      </c>
+      <c r="D540" s="3">
+        <v>5411913831</v>
+      </c>
+      <c r="E540" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F540" s="3" t="s">
+        <v>1014</v>
+      </c>
+      <c r="G540" s="3"/>
+      <c r="H540" s="3">
+        <v>11</v>
+      </c>
+      <c r="I540" s="3"/>
+      <c r="J540" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K540" s="3"/>
+      <c r="L540" s="3"/>
+      <c r="M540" s="3"/>
+    </row>
+    <row r="541" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A541" s="3" t="s">
+        <v>985</v>
+      </c>
+      <c r="B541" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C541" s="3">
+        <v>436998</v>
+      </c>
+      <c r="D541" s="3">
+        <v>5411947619</v>
+      </c>
+      <c r="E541" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F541" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="G541" s="3"/>
+      <c r="H541" s="3">
+        <v>25</v>
+      </c>
+      <c r="I541" s="3"/>
+      <c r="J541" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K541" s="3"/>
+      <c r="L541" s="3"/>
+      <c r="M541" s="3"/>
+    </row>
+    <row r="542" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A542" s="3" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B542" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C542" s="3">
+        <v>436998</v>
+      </c>
+      <c r="D542" s="3">
+        <v>5412037203</v>
+      </c>
+      <c r="E542" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F542" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="G542" s="3"/>
+      <c r="H542" s="3">
+        <v>11</v>
+      </c>
+      <c r="I542" s="3"/>
+      <c r="J542" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K542" s="3"/>
+      <c r="L542" s="3"/>
+      <c r="M542" s="3"/>
+    </row>
+    <row r="543" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A543" s="3" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B543" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C543" s="3">
+        <v>219022</v>
+      </c>
+      <c r="D543" s="3">
+        <v>5423222542</v>
+      </c>
+      <c r="E543" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F543" s="3" t="s">
+        <v>1017</v>
+      </c>
+      <c r="G543" s="3"/>
+      <c r="H543" s="3">
+        <v>54</v>
+      </c>
+      <c r="I543" s="3"/>
+      <c r="J543" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K543" s="3"/>
+      <c r="L543" s="3"/>
+      <c r="M543" s="3"/>
+    </row>
+    <row r="544" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A544" s="3" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B544" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C544" s="3">
+        <v>436998</v>
+      </c>
+      <c r="D544" s="3">
+        <v>5412569507</v>
+      </c>
+      <c r="E544" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F544" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G544" s="3"/>
+      <c r="H544" s="3">
+        <v>12</v>
+      </c>
+      <c r="I544" s="3"/>
+      <c r="J544" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K544" s="3"/>
+      <c r="L544" s="3"/>
+      <c r="M544" s="3"/>
+    </row>
+    <row r="545" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A545" s="3" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B545" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C545" s="3">
+        <v>596008</v>
+      </c>
+      <c r="D545" s="3">
+        <v>5412633313</v>
+      </c>
+      <c r="E545" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="F545" s="3" t="s">
+        <v>1020</v>
+      </c>
+      <c r="G545" s="3"/>
+      <c r="H545" s="3">
+        <v>14</v>
+      </c>
+      <c r="I545" s="3">
+        <v>65</v>
+      </c>
+      <c r="J545" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K545" s="3"/>
+      <c r="L545" s="3"/>
+      <c r="M545" s="3"/>
+    </row>
+    <row r="546" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A546" s="3" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B546" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C546" s="3">
+        <v>219022</v>
+      </c>
+      <c r="D546" s="3">
+        <v>5412847291</v>
+      </c>
+      <c r="E546" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F546" s="3" t="s">
+        <v>1022</v>
+      </c>
+      <c r="G546" s="3"/>
+      <c r="H546" s="3">
+        <v>39</v>
+      </c>
+      <c r="I546" s="3"/>
+      <c r="J546" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K546" s="3"/>
+      <c r="L546" s="3"/>
+      <c r="M546" s="3"/>
+    </row>
+    <row r="547" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A547" s="3" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B547" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C547" s="3">
+        <v>596008</v>
+      </c>
+      <c r="D547" s="3">
+        <v>5412880312</v>
+      </c>
+      <c r="E547" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F547" s="3" t="s">
+        <v>1024</v>
+      </c>
+      <c r="G547" s="3"/>
+      <c r="H547" s="3">
+        <v>50</v>
+      </c>
+      <c r="I547" s="3">
+        <v>65</v>
+      </c>
+      <c r="J547" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K547" s="3"/>
+      <c r="L547" s="3"/>
+      <c r="M547" s="3"/>
+    </row>
+    <row r="548" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A548" s="3" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B548" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C548" s="3">
+        <v>596008</v>
+      </c>
+      <c r="D548" s="3">
+        <v>5423176085</v>
+      </c>
+      <c r="E548" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F548" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="G548" s="3"/>
+      <c r="H548" s="3">
+        <v>17</v>
+      </c>
+      <c r="I548" s="3"/>
+      <c r="J548" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K548" s="3"/>
+      <c r="L548" s="3"/>
+      <c r="M548" s="3"/>
+    </row>
+    <row r="549" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A549" s="3" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B549" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C549" s="3">
+        <v>436998</v>
+      </c>
+      <c r="D549" s="3">
+        <v>5413897896</v>
+      </c>
+      <c r="E549" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F549" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="G549" s="3"/>
+      <c r="H549" s="3">
+        <v>12</v>
+      </c>
+      <c r="I549" s="3"/>
+      <c r="J549" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K549" s="3"/>
+      <c r="L549" s="3"/>
+      <c r="M549" s="3"/>
+    </row>
+    <row r="550" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A550" s="3" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B550" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C550" s="3">
+        <v>226259</v>
+      </c>
+      <c r="D550" s="3">
+        <v>5414310588</v>
+      </c>
+      <c r="E550" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F550" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="G550" s="3"/>
+      <c r="H550" s="3">
+        <v>52</v>
+      </c>
+      <c r="I550" s="3"/>
+      <c r="J550" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K550" s="3"/>
+      <c r="L550" s="3"/>
+      <c r="M550" s="3"/>
+    </row>
+    <row r="551" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A551" s="3" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B551" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C551" s="3">
+        <v>193270</v>
+      </c>
+      <c r="D551" s="3">
+        <v>5423214160</v>
+      </c>
+      <c r="E551" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F551" s="3" t="s">
+        <v>1029</v>
+      </c>
+      <c r="G551" s="3"/>
+      <c r="H551" s="3">
+        <v>24</v>
+      </c>
+      <c r="I551" s="3"/>
+      <c r="J551" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K551" s="3"/>
+      <c r="L551" s="3"/>
+      <c r="M551" s="3"/>
+    </row>
+    <row r="552" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A552" s="3" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B552" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C552" s="3">
+        <v>193270</v>
+      </c>
+      <c r="D552" s="3">
+        <v>5415624928</v>
+      </c>
+      <c r="E552" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F552" s="3" t="s">
+        <v>821</v>
+      </c>
+      <c r="G552" s="3"/>
+      <c r="H552" s="3">
+        <v>46</v>
+      </c>
+      <c r="I552" s="3"/>
+      <c r="J552" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K552" s="3"/>
+      <c r="L552" s="3"/>
+      <c r="M552" s="3"/>
+    </row>
+    <row r="553" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A553" s="3" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B553" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C553" s="3">
+        <v>193270</v>
+      </c>
+      <c r="D553" s="3">
+        <v>5423339658</v>
+      </c>
+      <c r="E553" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F553" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="G553" s="3"/>
+      <c r="H553" s="3">
+        <v>59</v>
+      </c>
+      <c r="I553" s="3"/>
+      <c r="J553" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K553" s="3"/>
+      <c r="L553" s="3"/>
+      <c r="M553" s="3"/>
+    </row>
+    <row r="554" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A554" s="3" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B554" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C554" s="3">
+        <v>436998</v>
+      </c>
+      <c r="D554" s="3">
+        <v>5417695490</v>
+      </c>
+      <c r="E554" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F554" s="3" t="s">
+        <v>1014</v>
+      </c>
+      <c r="G554" s="3"/>
+      <c r="H554" s="3">
+        <v>13</v>
+      </c>
+      <c r="I554" s="3"/>
+      <c r="J554" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K554" s="3"/>
+      <c r="L554" s="3"/>
+      <c r="M554" s="3"/>
+    </row>
+    <row r="555" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A555" s="3" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B555" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C555" s="3">
+        <v>436998</v>
+      </c>
+      <c r="D555" s="3">
+        <v>5417735932</v>
+      </c>
+      <c r="E555" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="F555" s="3" t="s">
+        <v>1034</v>
+      </c>
+      <c r="G555" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H555" s="3">
+        <v>19</v>
+      </c>
+      <c r="I555" s="3"/>
+      <c r="J555" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K555" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L555" s="3" t="s">
+        <v>1035</v>
+      </c>
+      <c r="M555" s="3"/>
+    </row>
+    <row r="556" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A556" s="3" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B556" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C556" s="3">
+        <v>226259</v>
+      </c>
+      <c r="D556" s="3">
+        <v>5417907259</v>
+      </c>
+      <c r="E556" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F556" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="G556" s="3"/>
+      <c r="H556" s="3">
+        <v>39</v>
+      </c>
+      <c r="I556" s="3"/>
+      <c r="J556" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K556" s="3"/>
+      <c r="L556" s="3"/>
+      <c r="M556" s="3"/>
+    </row>
+    <row r="557" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A557" s="3" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B557" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C557" s="3">
+        <v>193268</v>
+      </c>
+      <c r="D557" s="3">
+        <v>5417914381</v>
+      </c>
+      <c r="E557" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F557" s="3" t="s">
+        <v>1038</v>
+      </c>
+      <c r="G557" s="3"/>
+      <c r="H557" s="3">
+        <v>20</v>
+      </c>
+      <c r="I557" s="3"/>
+      <c r="J557" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K557" s="3"/>
+      <c r="L557" s="3"/>
+      <c r="M557" s="3"/>
+    </row>
+    <row r="558" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A558" s="3" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B558" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C558" s="3">
+        <v>436998</v>
+      </c>
+      <c r="D558" s="3">
+        <v>5417996653</v>
+      </c>
+      <c r="E558" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F558" s="3" t="s">
+        <v>1040</v>
+      </c>
+      <c r="G558" s="3"/>
+      <c r="H558" s="3">
+        <v>16</v>
+      </c>
+      <c r="I558" s="3"/>
+      <c r="J558" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K558" s="3"/>
+      <c r="L558" s="3"/>
+      <c r="M558" s="3"/>
+    </row>
+    <row r="559" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A559" s="3" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B559" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C559" s="3">
+        <v>436998</v>
+      </c>
+      <c r="D559" s="3">
+        <v>5418233047</v>
+      </c>
+      <c r="E559" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F559" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="G559" s="3"/>
+      <c r="H559" s="3">
+        <v>14</v>
+      </c>
+      <c r="I559" s="3"/>
+      <c r="J559" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K559" s="3"/>
+      <c r="L559" s="3"/>
+      <c r="M559" s="3"/>
+    </row>
+    <row r="560" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A560" s="3" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B560" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C560" s="3">
+        <v>596008</v>
+      </c>
+      <c r="D560" s="3">
+        <v>5418458533</v>
+      </c>
+      <c r="E560" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="F560" s="3" t="s">
+        <v>1043</v>
+      </c>
+      <c r="G560" s="3"/>
+      <c r="H560" s="3">
+        <v>57</v>
+      </c>
+      <c r="I560" s="3">
+        <v>65</v>
+      </c>
+      <c r="J560" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K560" s="3"/>
+      <c r="L560" s="3"/>
+      <c r="M560" s="3"/>
+    </row>
+    <row r="561" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A561" s="3" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B561" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C561" s="3">
+        <v>436998</v>
+      </c>
+      <c r="D561" s="3">
+        <v>5418927981</v>
+      </c>
+      <c r="E561" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F561" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G561" s="3"/>
+      <c r="H561" s="3">
+        <v>14</v>
+      </c>
+      <c r="I561" s="3"/>
+      <c r="J561" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K561" s="3"/>
+      <c r="L561" s="3"/>
+      <c r="M561" s="3"/>
+    </row>
+    <row r="562" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A562" s="3" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B562" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C562" s="3">
+        <v>436998</v>
+      </c>
+      <c r="D562" s="3">
+        <v>5419207916</v>
+      </c>
+      <c r="E562" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F562" s="3" t="s">
+        <v>1046</v>
+      </c>
+      <c r="G562" s="3"/>
+      <c r="H562" s="3">
+        <v>57</v>
+      </c>
+      <c r="I562" s="3"/>
+      <c r="J562" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K562" s="3"/>
+      <c r="L562" s="3"/>
+      <c r="M562" s="3"/>
+    </row>
+    <row r="563" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A563" s="3" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B563" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C563" s="3">
+        <v>436998</v>
+      </c>
+      <c r="D563" s="3">
+        <v>5419326279</v>
+      </c>
+      <c r="E563" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F563" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G563" s="3"/>
+      <c r="H563" s="3">
+        <v>43</v>
+      </c>
+      <c r="I563" s="3"/>
+      <c r="J563" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K563" s="3"/>
+      <c r="L563" s="3"/>
+      <c r="M563" s="3"/>
+    </row>
+    <row r="564" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A564" s="3" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B564" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C564" s="3">
+        <v>436998</v>
+      </c>
+      <c r="D564" s="3">
+        <v>5419349105</v>
+      </c>
+      <c r="E564" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F564" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G564" s="3"/>
+      <c r="H564" s="3">
+        <v>9</v>
+      </c>
+      <c r="I564" s="3"/>
+      <c r="J564" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K564" s="3"/>
+      <c r="L564" s="3"/>
+      <c r="M564" s="3"/>
+    </row>
+    <row r="565" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A565" s="3" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B565" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C565" s="3">
+        <v>193268</v>
+      </c>
+      <c r="D565" s="3">
+        <v>5419587443</v>
+      </c>
+      <c r="E565" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F565" s="3" t="s">
+        <v>1050</v>
+      </c>
+      <c r="G565" s="3"/>
+      <c r="H565" s="3">
+        <v>16</v>
+      </c>
+      <c r="I565" s="3"/>
+      <c r="J565" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K565" s="3"/>
+      <c r="L565" s="3"/>
+      <c r="M565" s="3"/>
+    </row>
+    <row r="566" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A566" s="3" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B566" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C566" s="3">
+        <v>193268</v>
+      </c>
+      <c r="D566" s="3">
+        <v>5429564588</v>
+      </c>
+      <c r="E566" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F566" s="3" t="s">
+        <v>1052</v>
+      </c>
+      <c r="G566" s="3"/>
+      <c r="H566" s="3">
+        <v>59</v>
+      </c>
+      <c r="I566" s="3">
+        <v>70</v>
+      </c>
+      <c r="J566" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K566" s="3"/>
+      <c r="L566" s="3"/>
+      <c r="M566" s="3"/>
+    </row>
+    <row r="567" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A567" s="3" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B567" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C567" s="3">
+        <v>226259</v>
+      </c>
+      <c r="D567" s="3">
+        <v>5420898601</v>
+      </c>
+      <c r="E567" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F567" s="3" t="s">
+        <v>1054</v>
+      </c>
+      <c r="G567" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H567" s="3">
+        <v>30</v>
+      </c>
+      <c r="I567" s="3"/>
+      <c r="J567" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K567" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L567" s="3" t="s">
+        <v>1055</v>
+      </c>
+      <c r="M567" s="3" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="568" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A568" s="3" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B568" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C568" s="3">
+        <v>403744</v>
+      </c>
+      <c r="D568" s="3">
+        <v>5420909041</v>
+      </c>
+      <c r="E568" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F568" s="3" t="s">
+        <v>1058</v>
+      </c>
+      <c r="G568" s="3" t="s">
+        <v>1059</v>
+      </c>
+      <c r="H568" s="3">
+        <v>16</v>
+      </c>
+      <c r="I568" s="3"/>
+      <c r="J568" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K568" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L568" s="3" t="s">
+        <v>1060</v>
+      </c>
+      <c r="M568" s="3"/>
+    </row>
+    <row r="569" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A569" s="3" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B569" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C569" s="3">
+        <v>436998</v>
+      </c>
+      <c r="D569" s="3">
+        <v>5423862807</v>
+      </c>
+      <c r="E569" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F569" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="G569" s="3"/>
+      <c r="H569" s="3">
+        <v>17</v>
+      </c>
+      <c r="I569" s="3"/>
+      <c r="J569" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K569" s="3"/>
+      <c r="L569" s="3"/>
+      <c r="M569" s="3"/>
+    </row>
+    <row r="570" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A570" s="3" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B570" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C570" s="3">
+        <v>596008</v>
+      </c>
+      <c r="D570" s="3">
+        <v>5435914159</v>
+      </c>
+      <c r="E570" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F570" s="3" t="s">
+        <v>1063</v>
+      </c>
+      <c r="G570" s="3"/>
+      <c r="H570" s="3"/>
+      <c r="I570" s="3"/>
+      <c r="J570" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K570" s="3"/>
+      <c r="L570" s="3"/>
+      <c r="M570" s="3"/>
+    </row>
+    <row r="571" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A571" s="3" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B571" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C571" s="3">
+        <v>219022</v>
+      </c>
+      <c r="D571" s="3">
+        <v>5435875111</v>
+      </c>
+      <c r="E571" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F571" s="3" t="s">
+        <v>1064</v>
+      </c>
+      <c r="G571" s="3"/>
+      <c r="H571" s="3">
+        <v>34</v>
+      </c>
+      <c r="I571" s="3">
+        <v>65</v>
+      </c>
+      <c r="J571" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K571" s="3"/>
+      <c r="L571" s="3"/>
+      <c r="M571" s="3"/>
+    </row>
+    <row r="572" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A572" s="3" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B572" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C572" s="3">
+        <v>596008</v>
+      </c>
+      <c r="D572" s="3">
+        <v>5424714371</v>
+      </c>
+      <c r="E572" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="F572" s="3" t="s">
+        <v>1043</v>
+      </c>
+      <c r="G572" s="3"/>
+      <c r="H572" s="3">
+        <v>55</v>
+      </c>
+      <c r="I572" s="3">
+        <v>65</v>
+      </c>
+      <c r="J572" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K572" s="3"/>
+      <c r="L572" s="3"/>
+      <c r="M572" s="3"/>
+    </row>
+    <row r="573" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A573" s="3" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B573" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C573" s="3">
+        <v>436998</v>
+      </c>
+      <c r="D573" s="3">
+        <v>5426579995</v>
+      </c>
+      <c r="E573" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F573" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="G573" s="3"/>
+      <c r="H573" s="3">
+        <v>17</v>
+      </c>
+      <c r="I573" s="3"/>
+      <c r="J573" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K573" s="3"/>
+      <c r="L573" s="3"/>
+      <c r="M573" s="3"/>
+    </row>
+    <row r="574" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A574" s="3" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B574" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C574" s="3">
+        <v>436998</v>
+      </c>
+      <c r="D574" s="3">
+        <v>5427074267</v>
+      </c>
+      <c r="E574" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F574" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="G574" s="3"/>
+      <c r="H574" s="3">
+        <v>34</v>
+      </c>
+      <c r="I574" s="3"/>
+      <c r="J574" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K574" s="3"/>
+      <c r="L574" s="3"/>
+      <c r="M574" s="3"/>
+    </row>
+    <row r="575" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A575" s="3" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B575" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C575" s="3">
+        <v>436998</v>
+      </c>
+      <c r="D575" s="3">
+        <v>5427082788</v>
+      </c>
+      <c r="E575" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F575" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="G575" s="3"/>
+      <c r="H575" s="3">
+        <v>26</v>
+      </c>
+      <c r="I575" s="3"/>
+      <c r="J575" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K575" s="3"/>
+      <c r="L575" s="3"/>
+      <c r="M575" s="3"/>
+    </row>
+    <row r="576" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A576" s="3" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B576" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C576" s="3">
+        <v>226259</v>
+      </c>
+      <c r="D576" s="3">
+        <v>5430006071</v>
+      </c>
+      <c r="E576" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="F576" s="3" t="s">
+        <v>1070</v>
+      </c>
+      <c r="G576" s="3"/>
+      <c r="H576" s="3">
+        <v>52</v>
+      </c>
+      <c r="I576" s="3">
+        <v>65</v>
+      </c>
+      <c r="J576" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K576" s="3"/>
+      <c r="L576" s="3"/>
+      <c r="M576" s="3"/>
+    </row>
+    <row r="577" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A577" s="3" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B577" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C577" s="3">
+        <v>226259</v>
+      </c>
+      <c r="D577" s="3">
+        <v>5430065444</v>
+      </c>
+      <c r="E577" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="F577" s="3" t="s">
+        <v>1072</v>
+      </c>
+      <c r="G577" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H577" s="3">
+        <v>57</v>
+      </c>
+      <c r="I577" s="3"/>
+      <c r="J577" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K577" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L577" s="3" t="s">
+        <v>1073</v>
+      </c>
+      <c r="M577" s="3"/>
+    </row>
+    <row r="578" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A578" s="3" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B578" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C578" s="3">
+        <v>436998</v>
+      </c>
+      <c r="D578" s="3">
+        <v>5430141579</v>
+      </c>
+      <c r="E578" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F578" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="G578" s="3"/>
+      <c r="H578" s="3">
+        <v>22</v>
+      </c>
+      <c r="I578" s="3"/>
+      <c r="J578" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K578" s="3"/>
+      <c r="L578" s="3"/>
+      <c r="M578" s="3"/>
+    </row>
+    <row r="579" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A579" s="3" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B579" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C579" s="3">
+        <v>226259</v>
+      </c>
+      <c r="D579" s="3">
+        <v>5430144098</v>
+      </c>
+      <c r="E579" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F579" s="3" t="s">
+        <v>1076</v>
+      </c>
+      <c r="G579" s="3"/>
+      <c r="H579" s="3">
+        <v>26</v>
+      </c>
+      <c r="I579" s="3"/>
+      <c r="J579" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K579" s="3"/>
+      <c r="L579" s="3"/>
+      <c r="M579" s="3"/>
+    </row>
+    <row r="580" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A580" s="3" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B580" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C580" s="3">
+        <v>219022</v>
+      </c>
+      <c r="D580" s="3">
+        <v>5441922504</v>
+      </c>
+      <c r="E580" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F580" s="3" t="s">
+        <v>1078</v>
+      </c>
+      <c r="G580" s="3"/>
+      <c r="H580" s="3">
+        <v>47</v>
+      </c>
+      <c r="I580" s="3"/>
+      <c r="J580" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K580" s="3"/>
+      <c r="L580" s="3"/>
+      <c r="M580" s="3"/>
+    </row>
+    <row r="581" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A581" s="3" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B581" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C581" s="3">
+        <v>226260</v>
+      </c>
+      <c r="D581" s="3">
+        <v>5441830925</v>
+      </c>
+      <c r="E581" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F581" s="3" t="s">
+        <v>1080</v>
+      </c>
+      <c r="G581" s="3"/>
+      <c r="H581" s="3">
+        <v>51</v>
+      </c>
+      <c r="I581" s="3">
+        <v>65</v>
+      </c>
+      <c r="J581" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K581" s="3"/>
+      <c r="L581" s="3"/>
+      <c r="M581" s="3"/>
+    </row>
+    <row r="582" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A582" s="3" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B582" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C582" s="3">
+        <v>436998</v>
+      </c>
+      <c r="D582" s="3">
+        <v>5431039722</v>
+      </c>
+      <c r="E582" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F582" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G582" s="3"/>
+      <c r="H582" s="3">
+        <v>18</v>
+      </c>
+      <c r="I582" s="3"/>
+      <c r="J582" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K582" s="3"/>
+      <c r="L582" s="3"/>
+      <c r="M582" s="3"/>
+    </row>
+    <row r="583" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A583" s="3" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B583" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C583" s="3">
+        <v>436998</v>
+      </c>
+      <c r="D583" s="3">
+        <v>5431066382</v>
+      </c>
+      <c r="E583" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F583" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="G583" s="3"/>
+      <c r="H583" s="3">
+        <v>26</v>
+      </c>
+      <c r="I583" s="3"/>
+      <c r="J583" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K583" s="3"/>
+      <c r="L583" s="3"/>
+      <c r="M583" s="3"/>
+    </row>
+    <row r="584" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A584" s="3" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B584" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C584" s="3">
+        <v>436998</v>
+      </c>
+      <c r="D584" s="3">
+        <v>5432383108</v>
+      </c>
+      <c r="E584" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F584" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="G584" s="3"/>
+      <c r="H584" s="3"/>
+      <c r="I584" s="3"/>
+      <c r="J584" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K584" s="3"/>
+      <c r="L584" s="3"/>
+      <c r="M584" s="3"/>
+    </row>
+    <row r="585" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A585" s="3" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B585" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C585" s="3">
+        <v>226260</v>
+      </c>
+      <c r="D585" s="3">
+        <v>5432581090</v>
+      </c>
+      <c r="E585" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F585" s="3" t="s">
+        <v>1085</v>
+      </c>
+      <c r="G585" s="3"/>
+      <c r="H585" s="3">
+        <v>49</v>
+      </c>
+      <c r="I585" s="3"/>
+      <c r="J585" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K585" s="3"/>
+      <c r="L585" s="3"/>
+      <c r="M585" s="3"/>
+    </row>
+    <row r="586" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A586" s="3" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B586" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C586" s="3">
+        <v>436998</v>
+      </c>
+      <c r="D586" s="3">
+        <v>5442012469</v>
+      </c>
+      <c r="E586" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F586" s="3" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G586" s="3"/>
+      <c r="H586" s="3"/>
+      <c r="I586" s="3"/>
+      <c r="J586" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K586" s="3"/>
+      <c r="L586" s="3"/>
+      <c r="M586" s="3"/>
+    </row>
+    <row r="587" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A587" s="3" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B587" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C587" s="3">
+        <v>436998</v>
+      </c>
+      <c r="D587" s="3">
+        <v>5433315176</v>
+      </c>
+      <c r="E587" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F587" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G587" s="3"/>
+      <c r="H587" s="3"/>
+      <c r="I587" s="3"/>
+      <c r="J587" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K587" s="3"/>
+      <c r="L587" s="3"/>
+      <c r="M587" s="3"/>
+    </row>
+    <row r="588" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A588" s="3" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B588" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C588" s="3">
+        <v>596008</v>
+      </c>
+      <c r="D588" s="3">
+        <v>5441900725</v>
+      </c>
+      <c r="E588" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F588" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="G588" s="3"/>
+      <c r="H588" s="3"/>
+      <c r="I588" s="3"/>
+      <c r="J588" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K588" s="3"/>
+      <c r="L588" s="3"/>
+      <c r="M588" s="3"/>
+    </row>
+    <row r="589" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A589" s="3" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B589" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C589" s="3">
+        <v>436998</v>
+      </c>
+      <c r="D589" s="3">
+        <v>5442131940</v>
+      </c>
+      <c r="E589" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F589" s="3" t="s">
+        <v>845</v>
+      </c>
+      <c r="G589" s="3"/>
+      <c r="H589" s="3"/>
+      <c r="I589" s="3"/>
+      <c r="J589" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K589" s="3"/>
+      <c r="L589" s="3"/>
+      <c r="M589" s="3"/>
+    </row>
+    <row r="590" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A590" s="3" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B590" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C590" s="3">
+        <v>226259</v>
+      </c>
+      <c r="D590" s="3">
+        <v>5436444297</v>
+      </c>
+      <c r="E590" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F590" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G590" s="3"/>
+      <c r="H590" s="3">
+        <v>38</v>
+      </c>
+      <c r="I590" s="3"/>
+      <c r="J590" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K590" s="3"/>
+      <c r="L590" s="3"/>
+      <c r="M590" s="3"/>
+    </row>
+    <row r="591" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A591" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B591" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C591" s="3">
+        <v>489766</v>
+      </c>
+      <c r="D591" s="3">
+        <v>5437305339</v>
+      </c>
+      <c r="E591" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="F591" s="3" t="s">
+        <v>1093</v>
+      </c>
+      <c r="G591" s="3"/>
+      <c r="H591" s="3"/>
+      <c r="I591" s="3"/>
+      <c r="J591" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K591" s="3"/>
+      <c r="L591" s="3"/>
+      <c r="M591" s="3"/>
+    </row>
+    <row r="592" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A592" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B592" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C592" s="3">
+        <v>226259</v>
+      </c>
+      <c r="D592" s="3">
+        <v>5439387686</v>
+      </c>
+      <c r="E592" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F592" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G592" s="3"/>
+      <c r="H592" s="3">
+        <v>6</v>
+      </c>
+      <c r="I592" s="3"/>
+      <c r="J592" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K592" s="3"/>
+      <c r="L592" s="3"/>
+      <c r="M592" s="3"/>
+    </row>
+    <row r="593" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A593" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B593" s="3" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C593" s="3">
+        <v>219023</v>
+      </c>
+      <c r="D593" s="3">
+        <v>5439560169</v>
+      </c>
+      <c r="E593" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F593" s="3" t="s">
+        <v>1097</v>
+      </c>
+      <c r="G593" s="3"/>
+      <c r="H593" s="3">
+        <v>54</v>
+      </c>
+      <c r="I593" s="3"/>
+      <c r="J593" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K593" s="3"/>
+      <c r="L593" s="3"/>
+      <c r="M593" s="3"/>
+    </row>
+    <row r="594" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A594" s="3" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B594" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C594" s="3">
+        <v>489766</v>
+      </c>
+      <c r="D594" s="3">
+        <v>5439577998</v>
+      </c>
+      <c r="E594" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F594" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G594" s="3"/>
+      <c r="H594" s="3"/>
+      <c r="I594" s="3"/>
+      <c r="J594" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K594" s="3"/>
+      <c r="L594" s="3"/>
+      <c r="M594" s="3"/>
+    </row>
+    <row r="595" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A595" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B595" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C595" s="3">
+        <v>489766</v>
+      </c>
+      <c r="D595" s="3">
+        <v>5442842269</v>
+      </c>
+      <c r="E595" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F595" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="G595" s="3"/>
+      <c r="H595" s="3"/>
+      <c r="I595" s="3"/>
+      <c r="J595" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K595" s="3"/>
+      <c r="L595" s="3"/>
+      <c r="M595" s="3"/>
+    </row>
+    <row r="596" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A596" s="3" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B596" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C596" s="3">
+        <v>596008</v>
+      </c>
+      <c r="D596" s="3">
+        <v>5442976452</v>
+      </c>
+      <c r="E596" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F596" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G596" s="3"/>
+      <c r="H596" s="3">
+        <v>24</v>
+      </c>
+      <c r="I596" s="3"/>
+      <c r="J596" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K596" s="3"/>
+      <c r="L596" s="3"/>
+      <c r="M596" s="3"/>
+    </row>
+    <row r="597" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A597" s="3" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B597" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C597" s="3">
+        <v>489766</v>
+      </c>
+      <c r="D597" s="3">
+        <v>5443116045</v>
+      </c>
+      <c r="E597" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F597" s="3" t="s">
+        <v>1103</v>
+      </c>
+      <c r="G597" s="3"/>
+      <c r="H597" s="3"/>
+      <c r="I597" s="3"/>
+      <c r="J597" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K597" s="3"/>
+      <c r="L597" s="3"/>
+      <c r="M597" s="3"/>
+    </row>
+    <row r="598" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A598" s="3" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B598" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C598" s="3">
+        <v>489766</v>
+      </c>
+      <c r="D598" s="3">
+        <v>5443350130</v>
+      </c>
+      <c r="E598" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F598" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G598" s="3"/>
+      <c r="H598" s="3"/>
+      <c r="I598" s="3"/>
+      <c r="J598" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K598" s="3"/>
+      <c r="L598" s="3"/>
+      <c r="M598" s="3"/>
+    </row>
+    <row r="599" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A599" s="3" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B599" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C599" s="3">
+        <v>170992</v>
+      </c>
+      <c r="D599" s="3">
+        <v>5443807942</v>
+      </c>
+      <c r="E599" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F599" s="3" t="s">
+        <v>1106</v>
+      </c>
+      <c r="G599" s="3"/>
+      <c r="H599" s="3">
+        <v>5</v>
+      </c>
+      <c r="I599" s="3"/>
+      <c r="J599" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K599" s="3"/>
+      <c r="L599" s="3"/>
+      <c r="M599" s="3"/>
+    </row>
+    <row r="600" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A600" s="3" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B600" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C600" s="3">
+        <v>170992</v>
+      </c>
+      <c r="D600" s="3">
+        <v>5444549118</v>
+      </c>
+      <c r="E600" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F600" s="3" t="s">
+        <v>1108</v>
+      </c>
+      <c r="G600" s="3"/>
+      <c r="H600" s="3">
+        <v>34</v>
+      </c>
+      <c r="I600" s="3"/>
+      <c r="J600" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K600" s="3"/>
+      <c r="L600" s="3"/>
+      <c r="M600" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
